--- a/salidas/empresas/MPC.xlsx
+++ b/salidas/empresas/MPC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B2" t="n">
-        <v>13.50287532806396</v>
+        <v>13.5028829574585</v>
       </c>
       <c r="C2" t="n">
         <v>20.70000076293945</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28239727020264</v>
+        <v>14.28239440917969</v>
       </c>
       <c r="C3" t="n">
         <v>21.89500045776367</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B4" t="n">
@@ -545,11 +557,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B5" t="n">
-        <v>8.873232841491699</v>
+        <v>8.873233795166016</v>
       </c>
       <c r="C5" t="n">
         <v>13.52999973297119</v>
@@ -570,7 +582,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B6" t="n">
@@ -595,11 +607,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0218563079834</v>
+        <v>11.02185916900635</v>
       </c>
       <c r="C7" t="n">
         <v>16.69499969482422</v>
@@ -620,11 +632,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B8" t="n">
-        <v>10.98884677886963</v>
+        <v>10.988844871521</v>
       </c>
       <c r="C8" t="n">
         <v>16.64500045776367</v>
@@ -645,11 +657,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B9" t="n">
-        <v>12.61621284484863</v>
+        <v>12.61621189117432</v>
       </c>
       <c r="C9" t="n">
         <v>19.11000061035156</v>
@@ -670,11 +682,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B10" t="n">
-        <v>13.79474449157715</v>
+        <v>13.79474353790283</v>
       </c>
       <c r="C10" t="n">
         <v>20.77499961853027</v>
@@ -699,7 +711,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B11" t="n">
@@ -728,11 +740,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B12" t="n">
-        <v>13.81466484069824</v>
+        <v>13.81466674804688</v>
       </c>
       <c r="C12" t="n">
         <v>20.80500030517578</v>
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B13" t="n">
@@ -786,11 +798,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B14" t="n">
-        <v>15.01446914672852</v>
+        <v>15.01447010040283</v>
       </c>
       <c r="C14" t="n">
         <v>22.45999908447266</v>
@@ -815,11 +827,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B15" t="n">
-        <v>15.80998420715332</v>
+        <v>15.80998134613037</v>
       </c>
       <c r="C15" t="n">
         <v>23.64999961853027</v>
@@ -844,11 +856,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B16" t="n">
-        <v>17.42041969299316</v>
+        <v>17.4204158782959</v>
       </c>
       <c r="C16" t="n">
         <v>25.875</v>
@@ -873,11 +885,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B17" t="n">
-        <v>18.37644004821777</v>
+        <v>18.37643623352051</v>
       </c>
       <c r="C17" t="n">
         <v>27.29500007629395</v>
@@ -902,11 +914,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B18" t="n">
-        <v>18.49088859558105</v>
+        <v>18.49088668823242</v>
       </c>
       <c r="C18" t="n">
         <v>27.46500015258789</v>
@@ -931,11 +943,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B19" t="n">
-        <v>20.17267417907715</v>
+        <v>20.17266464233398</v>
       </c>
       <c r="C19" t="n">
         <v>29.77000045776367</v>
@@ -960,7 +972,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B20" t="n">
@@ -989,11 +1001,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B21" t="n">
-        <v>25.14298820495605</v>
+        <v>25.14299201965332</v>
       </c>
       <c r="C21" t="n">
         <v>37.10499954223633</v>
@@ -1018,11 +1030,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B22" t="n">
-        <v>28.19914436340332</v>
+        <v>28.19913291931152</v>
       </c>
       <c r="C22" t="n">
         <v>41.43999862670898</v>
@@ -1047,11 +1059,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B23" t="n">
-        <v>30.48556327819824</v>
+        <v>30.48557472229004</v>
       </c>
       <c r="C23" t="n">
         <v>44.79999923706055</v>
@@ -1076,11 +1088,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B24" t="n">
-        <v>26.66126441955566</v>
+        <v>26.66125869750977</v>
       </c>
       <c r="C24" t="n">
         <v>39.18000030517578</v>
@@ -1105,11 +1117,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B25" t="n">
-        <v>28.19895935058594</v>
+        <v>28.19895172119141</v>
       </c>
       <c r="C25" t="n">
         <v>41.25</v>
@@ -1134,11 +1146,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B26" t="n">
-        <v>24.2887020111084</v>
+        <v>24.2887077331543</v>
       </c>
       <c r="C26" t="n">
         <v>35.52999877929688</v>
@@ -1163,11 +1175,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B27" t="n">
-        <v>25.06459426879883</v>
+        <v>25.0645923614502</v>
       </c>
       <c r="C27" t="n">
         <v>36.66500091552734</v>
@@ -1192,11 +1204,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B28" t="n">
-        <v>24.93392753601074</v>
+        <v>24.93392181396484</v>
       </c>
       <c r="C28" t="n">
         <v>36.25500106811523</v>
@@ -1221,11 +1233,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B29" t="n">
-        <v>22.11763763427734</v>
+        <v>22.11763572692871</v>
       </c>
       <c r="C29" t="n">
         <v>32.15999984741211</v>
@@ -1250,11 +1262,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B30" t="n">
-        <v>24.64163589477539</v>
+        <v>24.64162635803223</v>
       </c>
       <c r="C30" t="n">
         <v>35.83000183105469</v>
@@ -1279,11 +1291,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B31" t="n">
-        <v>28.60408210754395</v>
+        <v>28.60407638549805</v>
       </c>
       <c r="C31" t="n">
         <v>41.36999893188477</v>
@@ -1308,11 +1320,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B32" t="n">
-        <v>31.7120189666748</v>
+        <v>31.71200942993164</v>
       </c>
       <c r="C32" t="n">
         <v>45.8650016784668</v>
@@ -1337,11 +1349,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B33" t="n">
-        <v>30.09408569335938</v>
+        <v>30.09408950805664</v>
       </c>
       <c r="C33" t="n">
         <v>43.52500152587891</v>
@@ -1366,11 +1378,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B34" t="n">
-        <v>29.18288803100586</v>
+        <v>29.18289184570312</v>
       </c>
       <c r="C34" t="n">
         <v>42</v>
@@ -1395,11 +1407,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B35" t="n">
-        <v>30.23904037475586</v>
+        <v>30.23903656005859</v>
       </c>
       <c r="C35" t="n">
         <v>43.52000045776367</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B36" t="n">
-        <v>32.2922477722168</v>
+        <v>32.29226684570312</v>
       </c>
       <c r="C36" t="n">
         <v>46.47499847412109</v>
@@ -1453,11 +1465,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B37" t="n">
-        <v>31.20263481140137</v>
+        <v>31.20262336730957</v>
       </c>
       <c r="C37" t="n">
         <v>44.69499969482422</v>
@@ -1482,7 +1494,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B38" t="n">
@@ -1511,11 +1523,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B39" t="n">
-        <v>29.13968086242676</v>
+        <v>29.13966178894043</v>
       </c>
       <c r="C39" t="n">
         <v>41.7400016784668</v>
@@ -1540,11 +1552,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B40" t="n">
-        <v>31.94743347167969</v>
+        <v>31.94743156433105</v>
       </c>
       <c r="C40" t="n">
         <v>45.50500106811523</v>
@@ -1569,7 +1581,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B41" t="n">
@@ -1598,11 +1610,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B42" t="n">
-        <v>31.90881156921387</v>
+        <v>31.90882873535156</v>
       </c>
       <c r="C42" t="n">
         <v>45.45000076293945</v>
@@ -1627,11 +1639,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B43" t="n">
-        <v>31.79655647277832</v>
+        <v>31.79657554626465</v>
       </c>
       <c r="C43" t="n">
         <v>45.04499816894531</v>
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B44" t="n">
-        <v>31.8565788269043</v>
+        <v>31.8565731048584</v>
       </c>
       <c r="C44" t="n">
         <v>45.13000106811523</v>
@@ -1685,11 +1697,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B45" t="n">
-        <v>32.67892074584961</v>
+        <v>32.67891311645508</v>
       </c>
       <c r="C45" t="n">
         <v>46.29499816894531</v>
@@ -1714,11 +1726,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B46" t="n">
-        <v>37.24258041381836</v>
+        <v>37.24258804321289</v>
       </c>
       <c r="C46" t="n">
         <v>52.5</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B47" t="n">
-        <v>36.31684875488281</v>
+        <v>36.31682586669922</v>
       </c>
       <c r="C47" t="n">
         <v>51.19499969482422</v>
@@ -1772,11 +1784,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B48" t="n">
-        <v>34.9619140625</v>
+        <v>34.96192169189453</v>
       </c>
       <c r="C48" t="n">
         <v>49.28499984741211</v>
@@ -1801,11 +1813,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B49" t="n">
-        <v>36.87458038330078</v>
+        <v>36.87457656860352</v>
       </c>
       <c r="C49" t="n">
         <v>51.72999954223633</v>
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B50" t="n">
@@ -1859,11 +1871,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B51" t="n">
-        <v>38.97030258178711</v>
+        <v>38.97029113769531</v>
       </c>
       <c r="C51" t="n">
         <v>54.66999816894531</v>
@@ -1888,11 +1900,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B52" t="n">
-        <v>33.91889190673828</v>
+        <v>33.91889572143555</v>
       </c>
       <c r="C52" t="n">
         <v>47.31000137329102</v>
@@ -1917,7 +1929,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B53" t="n">
@@ -1946,11 +1958,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B54" t="n">
-        <v>37.13799667358398</v>
+        <v>37.13798522949219</v>
       </c>
       <c r="C54" t="n">
         <v>51.79999923706055</v>
@@ -1975,11 +1987,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B55" t="n">
-        <v>42.128173828125</v>
+        <v>42.12818145751953</v>
       </c>
       <c r="C55" t="n">
         <v>58.40999984741211</v>
@@ -2004,11 +2016,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B56" t="n">
-        <v>37.38957214355469</v>
+        <v>37.38956832885742</v>
       </c>
       <c r="C56" t="n">
         <v>51.84000015258789</v>
@@ -2033,11 +2045,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B57" t="n">
-        <v>30.14101409912109</v>
+        <v>30.1410083770752</v>
       </c>
       <c r="C57" t="n">
         <v>41.79000091552734</v>
@@ -2062,7 +2074,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B58" t="n">
@@ -2091,11 +2103,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B59" t="n">
-        <v>27.09730529785156</v>
+        <v>27.0973014831543</v>
       </c>
       <c r="C59" t="n">
         <v>37.18000030517578</v>
@@ -2120,11 +2132,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B60" t="n">
-        <v>28.4820556640625</v>
+        <v>28.4820499420166</v>
       </c>
       <c r="C60" t="n">
         <v>39.08000183105469</v>
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B61" t="n">
-        <v>25.61555099487305</v>
+        <v>25.61555290222168</v>
       </c>
       <c r="C61" t="n">
         <v>34.83000183105469</v>
@@ -2178,11 +2190,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B62" t="n">
-        <v>27.9174976348877</v>
+        <v>27.91750717163086</v>
       </c>
       <c r="C62" t="n">
         <v>37.95999908447266</v>
@@ -2207,11 +2219,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B63" t="n">
-        <v>28.96918106079102</v>
+        <v>28.96918296813965</v>
       </c>
       <c r="C63" t="n">
         <v>39.38999938964844</v>
@@ -2236,11 +2248,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B64" t="n">
-        <v>31.53596687316895</v>
+        <v>31.53597068786621</v>
       </c>
       <c r="C64" t="n">
         <v>42.5099983215332</v>
@@ -2265,11 +2277,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B65" t="n">
-        <v>30.11161994934082</v>
+        <v>30.11161804199219</v>
       </c>
       <c r="C65" t="n">
         <v>40.59000015258789</v>
@@ -2294,11 +2306,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B66" t="n">
-        <v>32.33715438842773</v>
+        <v>32.33716583251953</v>
       </c>
       <c r="C66" t="n">
         <v>43.59000015258789</v>
@@ -2323,11 +2335,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B67" t="n">
-        <v>35.16970825195312</v>
+        <v>35.16971588134766</v>
       </c>
       <c r="C67" t="n">
         <v>47.02000045776367</v>
@@ -2352,11 +2364,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B68" t="n">
-        <v>37.66045761108398</v>
+        <v>37.66046142578125</v>
       </c>
       <c r="C68" t="n">
         <v>50.34999847412109</v>
@@ -2381,11 +2393,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B69" t="n">
-        <v>35.94011688232422</v>
+        <v>35.94012451171875</v>
       </c>
       <c r="C69" t="n">
         <v>48.04999923706055</v>
@@ -2410,11 +2422,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B70" t="n">
-        <v>37.36703109741211</v>
+        <v>37.36702728271484</v>
       </c>
       <c r="C70" t="n">
         <v>49.59999847412109</v>
@@ -2439,11 +2451,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B71" t="n">
-        <v>38.07518005371094</v>
+        <v>38.07519912719727</v>
       </c>
       <c r="C71" t="n">
         <v>50.54000091552734</v>
@@ -2468,7 +2480,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B72" t="n">
@@ -2497,11 +2509,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B73" t="n">
-        <v>39.47506332397461</v>
+        <v>39.47505569458008</v>
       </c>
       <c r="C73" t="n">
         <v>52.04000091552734</v>
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B74" t="n">
-        <v>39.69503402709961</v>
+        <v>39.69503021240234</v>
       </c>
       <c r="C74" t="n">
         <v>52.33000183105469</v>
@@ -2555,11 +2567,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B75" t="n">
-        <v>42.47134399414062</v>
+        <v>42.47133255004883</v>
       </c>
       <c r="C75" t="n">
         <v>55.9900016784668</v>
@@ -2584,11 +2596,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B76" t="n">
-        <v>40.09354019165039</v>
+        <v>40.0935173034668</v>
       </c>
       <c r="C76" t="n">
         <v>52.45000076293945</v>
@@ -2613,11 +2625,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B77" t="n">
-        <v>42.86835098266602</v>
+        <v>42.86834716796875</v>
       </c>
       <c r="C77" t="n">
         <v>56.08000183105469</v>
@@ -2642,11 +2654,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B78" t="n">
-        <v>45.66612243652344</v>
+        <v>45.66611480712891</v>
       </c>
       <c r="C78" t="n">
         <v>59.7400016784668</v>
@@ -2671,11 +2683,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B79" t="n">
-        <v>48.18181228637695</v>
+        <v>48.18181610107422</v>
       </c>
       <c r="C79" t="n">
         <v>62.63000106811523</v>
@@ -2700,11 +2712,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B80" t="n">
-        <v>50.75899887084961</v>
+        <v>50.75900650024414</v>
       </c>
       <c r="C80" t="n">
         <v>65.98000335693359</v>
@@ -2729,11 +2741,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B81" t="n">
-        <v>53.29003143310547</v>
+        <v>53.2900276184082</v>
       </c>
       <c r="C81" t="n">
         <v>69.26999664306641</v>
@@ -2758,11 +2770,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B82" t="n">
-        <v>49.61792373657227</v>
+        <v>49.61791610717773</v>
       </c>
       <c r="C82" t="n">
         <v>64.05999755859375</v>
@@ -2787,11 +2799,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B83" t="n">
-        <v>56.62763595581055</v>
+        <v>56.62765884399414</v>
       </c>
       <c r="C83" t="n">
         <v>73.11000061035156</v>
@@ -2816,7 +2828,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B84" t="n">
@@ -2845,11 +2857,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B85" t="n">
-        <v>61.57455062866211</v>
+        <v>61.57456970214844</v>
       </c>
       <c r="C85" t="n">
         <v>79.02999877929688</v>
@@ -2874,11 +2886,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B86" t="n">
-        <v>54.66368865966797</v>
+        <v>54.66369247436523</v>
       </c>
       <c r="C86" t="n">
         <v>70.16000366210938</v>
@@ -2903,11 +2915,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B87" t="n">
-        <v>62.97699356079102</v>
+        <v>62.97698974609375</v>
       </c>
       <c r="C87" t="n">
         <v>80.83000183105469</v>
@@ -2932,11 +2944,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B88" t="n">
-        <v>64.48480224609375</v>
+        <v>64.48479461669922</v>
       </c>
       <c r="C88" t="n">
         <v>82.29000091552734</v>
@@ -2961,11 +2973,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B89" t="n">
-        <v>62.66678237915039</v>
+        <v>62.66677856445312</v>
       </c>
       <c r="C89" t="n">
         <v>79.97000122070312</v>
@@ -2990,11 +3002,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B90" t="n">
-        <v>55.20663070678711</v>
+        <v>55.20662307739258</v>
       </c>
       <c r="C90" t="n">
         <v>70.44999694824219</v>
@@ -3019,11 +3031,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B91" t="n">
-        <v>51.43437194824219</v>
+        <v>51.43436813354492</v>
       </c>
       <c r="C91" t="n">
         <v>65.16000366210938</v>
@@ -3048,11 +3060,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B92" t="n">
-        <v>46.57982635498047</v>
+        <v>46.57983779907227</v>
       </c>
       <c r="C92" t="n">
         <v>59.0099983215332</v>
@@ -3077,11 +3089,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B93" t="n">
-        <v>52.30265045166016</v>
+        <v>52.30265426635742</v>
       </c>
       <c r="C93" t="n">
         <v>66.26000213623047</v>
@@ -3106,11 +3118,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B94" t="n">
-        <v>49.34935760498047</v>
+        <v>49.3493537902832</v>
       </c>
       <c r="C94" t="n">
         <v>62.0099983215332</v>
@@ -3135,11 +3147,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B95" t="n">
-        <v>47.63035583496094</v>
+        <v>47.63036727905273</v>
       </c>
       <c r="C95" t="n">
         <v>59.84999847412109</v>
@@ -3164,11 +3176,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B96" t="n">
-        <v>48.44210052490234</v>
+        <v>48.44211196899414</v>
       </c>
       <c r="C96" t="n">
         <v>60.86999893188477</v>
@@ -3193,11 +3205,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B97" t="n">
-        <v>36.982177734375</v>
+        <v>36.98217010498047</v>
       </c>
       <c r="C97" t="n">
         <v>45.9900016784668</v>
@@ -3222,11 +3234,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B98" t="n">
-        <v>44.93507385253906</v>
+        <v>44.93508529663086</v>
       </c>
       <c r="C98" t="n">
         <v>55.88000106811523</v>
@@ -3251,7 +3263,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B99" t="n">
@@ -3280,11 +3292,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B100" t="n">
-        <v>40.01507949829102</v>
+        <v>40.01508712768555</v>
       </c>
       <c r="C100" t="n">
         <v>49.20999908447266</v>
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B101" t="n">
-        <v>49.39882278442383</v>
+        <v>49.39882659912109</v>
       </c>
       <c r="C101" t="n">
         <v>60.75</v>
@@ -3338,11 +3350,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B102" t="n">
-        <v>52.00089263916016</v>
+        <v>52.00090789794922</v>
       </c>
       <c r="C102" t="n">
         <v>63.95000076293945</v>
@@ -3367,11 +3379,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B103" t="n">
-        <v>49.71765518188477</v>
+        <v>49.71765899658203</v>
       </c>
       <c r="C103" t="n">
         <v>60.63999938964844</v>
@@ -3396,7 +3408,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B104" t="n">
@@ -3425,11 +3437,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B105" t="n">
-        <v>44.6835823059082</v>
+        <v>44.68357086181641</v>
       </c>
       <c r="C105" t="n">
         <v>54.5</v>
@@ -3454,11 +3466,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B106" t="n">
-        <v>39.26929092407227</v>
+        <v>39.26927947998047</v>
       </c>
       <c r="C106" t="n">
         <v>47.41999816894531</v>
@@ -3483,7 +3495,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B107" t="n">
@@ -3512,11 +3524,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B108" t="n">
-        <v>26.56598091125488</v>
+        <v>26.56598281860352</v>
       </c>
       <c r="C108" t="n">
         <v>32.08000183105469</v>
@@ -3541,7 +3553,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B109" t="n">
@@ -3568,11 +3580,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B110" t="n">
-        <v>31.47737121582031</v>
+        <v>31.47736930847168</v>
       </c>
       <c r="C110" t="n">
         <v>37.38000106811523</v>
@@ -3595,11 +3607,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B111" t="n">
-        <v>32.16788864135742</v>
+        <v>32.16788482666016</v>
       </c>
       <c r="C111" t="n">
         <v>38.20000076293945</v>
@@ -3622,11 +3634,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B112" t="n">
-        <v>30.31548309326172</v>
+        <v>30.31547927856445</v>
       </c>
       <c r="C112" t="n">
         <v>35.45999908447266</v>
@@ -3649,11 +3661,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B113" t="n">
-        <v>25.08336448669434</v>
+        <v>25.08336639404297</v>
       </c>
       <c r="C113" t="n">
         <v>29.34000015258789</v>
@@ -3676,11 +3688,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B114" t="n">
-        <v>25.22015762329102</v>
+        <v>25.22015380859375</v>
       </c>
       <c r="C114" t="n">
         <v>29.5</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B115" t="n">
-        <v>33.71948623657227</v>
+        <v>33.719482421875</v>
       </c>
       <c r="C115" t="n">
         <v>38.88000106811523</v>
@@ -3730,11 +3742,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B116" t="n">
-        <v>35.87031555175781</v>
+        <v>35.87031173706055</v>
       </c>
       <c r="C116" t="n">
         <v>41.36000061035156</v>
@@ -3757,11 +3769,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B117" t="n">
-        <v>37.43140029907227</v>
+        <v>37.43140411376953</v>
       </c>
       <c r="C117" t="n">
         <v>43.15999984741211</v>
@@ -3784,7 +3796,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B118" t="n">
@@ -3811,7 +3823,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B119" t="n">
@@ -3838,7 +3850,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B120" t="n">
@@ -3865,11 +3877,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B121" t="n">
-        <v>54.73659515380859</v>
+        <v>54.73659133911133</v>
       </c>
       <c r="C121" t="n">
         <v>61.79999923706055</v>
@@ -3892,11 +3904,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B122" t="n">
-        <v>53.51432418823242</v>
+        <v>53.51432800292969</v>
       </c>
       <c r="C122" t="n">
         <v>60.41999816894531</v>
@@ -3919,11 +3931,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B123" t="n">
-        <v>48.90865325927734</v>
+        <v>48.90865707397461</v>
       </c>
       <c r="C123" t="n">
         <v>55.22000122070312</v>
@@ -3946,7 +3958,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B124" t="n">
@@ -3975,11 +3987,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B125" t="n">
-        <v>55.29479598999023</v>
+        <v>55.29480361938477</v>
       </c>
       <c r="C125" t="n">
         <v>61.81000137329102</v>
@@ -4004,11 +4016,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B126" t="n">
-        <v>58.98052215576172</v>
+        <v>58.98053359985352</v>
       </c>
       <c r="C126" t="n">
         <v>65.93000030517578</v>
@@ -4033,11 +4045,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B127" t="n">
-        <v>54.91773223876953</v>
+        <v>54.91772079467773</v>
       </c>
       <c r="C127" t="n">
         <v>60.84999847412109</v>
@@ -4062,11 +4074,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B128" t="n">
-        <v>57.75160980224609</v>
+        <v>57.75161361694336</v>
       </c>
       <c r="C128" t="n">
         <v>63.9900016784668</v>
@@ -4091,11 +4103,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B129" t="n">
-        <v>64.75508117675781</v>
+        <v>64.75506591796875</v>
       </c>
       <c r="C129" t="n">
         <v>71.75</v>
@@ -4120,11 +4132,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B130" t="n">
-        <v>70.79716491699219</v>
+        <v>70.79717254638672</v>
       </c>
       <c r="C130" t="n">
         <v>77.87000274658203</v>
@@ -4149,11 +4161,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B131" t="n">
-        <v>77.73415374755859</v>
+        <v>77.73416137695312</v>
       </c>
       <c r="C131" t="n">
         <v>85.5</v>
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B132" t="n">
-        <v>79.33428192138672</v>
+        <v>79.33430480957031</v>
       </c>
       <c r="C132" t="n">
         <v>87.26000213623047</v>
@@ -4207,11 +4219,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B133" t="n">
-        <v>93.10431671142578</v>
+        <v>93.10432434082031</v>
       </c>
       <c r="C133" t="n">
         <v>101.7900009155273</v>
@@ -4236,11 +4248,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B134" t="n">
-        <v>75.19505310058594</v>
+        <v>75.19507598876953</v>
       </c>
       <c r="C134" t="n">
         <v>82.20999908447266</v>
@@ -4265,7 +4277,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B135" t="n">
@@ -4294,11 +4306,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B136" t="n">
-        <v>92.71444702148438</v>
+        <v>92.71445465087891</v>
       </c>
       <c r="C136" t="n">
         <v>100.75</v>
@@ -4323,7 +4335,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B137" t="n">
@@ -4352,11 +4364,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B138" t="n">
-        <v>104.5579528808594</v>
+        <v>104.5579681396484</v>
       </c>
       <c r="C138" t="n">
         <v>113.620002746582</v>
@@ -4381,11 +4393,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B139" t="n">
-        <v>112.7966232299805</v>
+        <v>112.7966384887695</v>
       </c>
       <c r="C139" t="n">
         <v>121.8099975585938</v>
@@ -4410,7 +4422,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B140" t="n">
@@ -4439,7 +4451,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B141" t="n">
@@ -4468,11 +4480,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B142" t="n">
-        <v>115.1253890991211</v>
+        <v>115.1253814697266</v>
       </c>
       <c r="C142" t="n">
         <v>123.5999984741211</v>
@@ -4497,11 +4509,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B143" t="n">
-        <v>125.5854034423828</v>
+        <v>125.5853805541992</v>
       </c>
       <c r="C143" t="n">
         <v>134.8300018310547</v>
@@ -4526,11 +4538,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B144" t="n">
-        <v>113.6350936889648</v>
+        <v>113.6350860595703</v>
       </c>
       <c r="C144" t="n">
         <v>122</v>
@@ -4555,11 +4567,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B145" t="n">
-        <v>98.38385009765625</v>
+        <v>98.38385772705078</v>
       </c>
       <c r="C145" t="n">
         <v>104.9100036621094</v>
@@ -4584,11 +4596,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B146" t="n">
-        <v>109.3466262817383</v>
+        <v>109.3466491699219</v>
       </c>
       <c r="C146" t="n">
         <v>116.5999984741211</v>
@@ -4613,11 +4625,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B147" t="n">
-        <v>124.7452087402344</v>
+        <v>124.7452163696289</v>
       </c>
       <c r="C147" t="n">
         <v>133.0200042724609</v>
@@ -4642,11 +4654,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B148" t="n">
-        <v>134.5681610107422</v>
+        <v>134.5681304931641</v>
       </c>
       <c r="C148" t="n">
         <v>142.7700042724609</v>
@@ -4671,11 +4683,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B149" t="n">
-        <v>142.6458282470703</v>
+        <v>142.6457977294922</v>
       </c>
       <c r="C149" t="n">
         <v>151.3399963378906</v>
@@ -4700,7 +4712,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B150" t="n">
@@ -4729,11 +4741,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B151" t="n">
-        <v>141.3935241699219</v>
+        <v>141.3935546875</v>
       </c>
       <c r="C151" t="n">
         <v>149.1900024414062</v>
@@ -4758,11 +4770,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B152" t="n">
-        <v>140.6069030761719</v>
+        <v>140.6068878173828</v>
       </c>
       <c r="C152" t="n">
         <v>148.3600006103516</v>
@@ -4787,7 +4799,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B153" t="n">
@@ -4816,11 +4828,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B154" t="n">
-        <v>161.1683654785156</v>
+        <v>161.1683502197266</v>
       </c>
       <c r="C154" t="n">
         <v>169.2299957275391</v>
@@ -4845,11 +4857,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B155" t="n">
-        <v>191.901123046875</v>
+        <v>191.9011077880859</v>
       </c>
       <c r="C155" t="n">
         <v>201.5</v>
@@ -4874,7 +4886,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B156" t="n">
@@ -4903,7 +4915,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B157" t="n">
@@ -4932,11 +4944,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B158" t="n">
-        <v>166.0006713867188</v>
+        <v>166.0006561279297</v>
       </c>
       <c r="C158" t="n">
         <v>173.4799957275391</v>
@@ -4961,11 +4973,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B159" t="n">
-        <v>169.3880615234375</v>
+        <v>169.3880310058594</v>
       </c>
       <c r="C159" t="n">
         <v>177.0200042724609</v>
@@ -4990,7 +5002,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B160" t="n">
@@ -5019,11 +5031,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B161" t="n">
-        <v>156.6394348144531</v>
+        <v>156.639404296875</v>
       </c>
       <c r="C161" t="n">
         <v>162.9100036621094</v>
@@ -5048,11 +5060,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B162" t="n">
-        <v>139.8707122802734</v>
+        <v>139.8706970214844</v>
       </c>
       <c r="C162" t="n">
         <v>145.4700012207031</v>
@@ -5077,11 +5089,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B163" t="n">
-        <v>151.0049591064453</v>
+        <v>151.0049285888672</v>
       </c>
       <c r="C163" t="n">
         <v>156.1499938964844</v>
@@ -5106,7 +5118,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B164" t="n">
@@ -5135,11 +5147,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B165" t="n">
-        <v>140.9089202880859</v>
+        <v>140.908935546875</v>
       </c>
       <c r="C165" t="n">
         <v>145.7100067138672</v>
@@ -5164,11 +5176,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B166" t="n">
-        <v>146.0674896240234</v>
+        <v>146.0674743652344</v>
       </c>
       <c r="C166" t="n">
         <v>150.1799926757812</v>
@@ -5193,11 +5205,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B167" t="n">
-        <v>141.700439453125</v>
+        <v>141.7004241943359</v>
       </c>
       <c r="C167" t="n">
         <v>145.6900024414062</v>
@@ -5222,11 +5234,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B168" t="n">
-        <v>133.6471710205078</v>
+        <v>133.6471557617188</v>
       </c>
       <c r="C168" t="n">
         <v>137.4100036621094</v>
@@ -5251,11 +5263,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B169" t="n">
-        <v>157.2240600585938</v>
+        <v>157.2240295410156</v>
       </c>
       <c r="C169" t="n">
         <v>160.7400054931641</v>
@@ -5280,7 +5292,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B170" t="n">
@@ -5309,7 +5321,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B171" t="n">
@@ -5338,11 +5350,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B172" t="n">
-        <v>176.7576141357422</v>
+        <v>176.7576446533203</v>
       </c>
       <c r="C172" t="n">
         <v>179.7100067138672</v>
@@ -5367,7 +5379,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B173" t="n">
@@ -5396,11 +5408,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B174" t="n">
-        <v>191.7079162597656</v>
+        <v>191.7079010009766</v>
       </c>
       <c r="C174" t="n">
         <v>194.9100036621094</v>
@@ -5425,11 +5437,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B175" t="n">
-        <v>191.5066986083984</v>
+        <v>191.5067138671875</v>
       </c>
       <c r="C175" t="n">
         <v>193.7299957275391</v>
@@ -5454,7 +5466,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B176" t="n">
@@ -5483,7 +5495,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B177" t="n">
@@ -5512,7 +5524,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B178" t="n">
@@ -5541,7 +5553,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B179" t="n">
@@ -5570,7 +5582,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B180" t="n">
@@ -5599,7 +5611,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B181" t="n">
@@ -5628,7 +5640,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B182" t="n">
@@ -5657,7 +5669,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B183" t="n">
@@ -5686,7 +5698,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B184" t="n">
@@ -5715,32 +5727,32 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B185" t="n">
-        <v>388.3800048828125</v>
+        <v>390.9500122070312</v>
       </c>
       <c r="C185" t="n">
-        <v>388.3800048828125</v>
+        <v>390.9500122070312</v>
       </c>
       <c r="D185" t="n">
-        <v>52726200</v>
+        <v>54816400</v>
       </c>
       <c r="E185" t="n">
         <v>28.96</v>
       </c>
       <c r="F185" t="n">
-        <v>13.41091177081535</v>
+        <v>13.49965511764611</v>
       </c>
       <c r="G185" t="n">
         <v>280824763</v>
       </c>
       <c r="H185" t="n">
-        <v>109066722825.1547</v>
+        <v>109788444522.8867</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1877548099274992</v>
+        <v>0.1951978857363088</v>
       </c>
     </row>
   </sheetData>
@@ -5772,75 +5784,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5876,13 +5888,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5918,13 +5930,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5960,13 +5972,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5993,7 +6005,7 @@
       <c r="I5" t="n">
         <v>0.865</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K5" t="n">
@@ -6006,13 +6018,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6039,7 +6051,7 @@
       <c r="I6" t="n">
         <v>2.01</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K6" t="n">
@@ -6052,13 +6064,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6085,7 +6097,7 @@
       <c r="I7" t="n">
         <v>2.565</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K7" t="n">
@@ -6098,13 +6110,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6131,7 +6143,7 @@
       <c r="I8" t="n">
         <v>3.760000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K8" t="n">
@@ -6144,13 +6156,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6177,7 +6189,7 @@
       <c r="I9" t="n">
         <v>3.335</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K9" t="n">
@@ -6190,13 +6202,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6223,7 +6235,7 @@
       <c r="I10" t="n">
         <v>3.445</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="K10" t="n">
@@ -6236,13 +6248,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6269,7 +6281,7 @@
       <c r="I11" t="n">
         <v>3.515</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K11" t="n">
@@ -6282,13 +6294,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6315,7 +6327,7 @@
       <c r="I12" t="n">
         <v>3.73</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="K12" t="n">
@@ -6328,13 +6340,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6361,7 +6373,7 @@
       <c r="I13" t="n">
         <v>4.955</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K13" t="n">
@@ -6374,13 +6386,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6407,7 +6419,7 @@
       <c r="I14" t="n">
         <v>5.19</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K14" t="n">
@@ -6420,13 +6432,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6453,7 +6465,7 @@
       <c r="I15" t="n">
         <v>4.915</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K15" t="n">
@@ -6466,13 +6478,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6499,7 +6511,7 @@
       <c r="I16" t="n">
         <v>3.39</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K16" t="n">
@@ -6512,13 +6524,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6545,7 +6557,7 @@
       <c r="I17" t="n">
         <v>3.305</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K17" t="n">
@@ -6558,13 +6570,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6591,7 +6603,7 @@
       <c r="I18" t="n">
         <v>2.555</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K18" t="n">
@@ -6604,13 +6616,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6637,7 +6649,7 @@
       <c r="I19" t="n">
         <v>3.115</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K19" t="n">
@@ -6650,13 +6662,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6683,7 +6695,7 @@
       <c r="I20" t="n">
         <v>4.024999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K20" t="n">
@@ -6696,13 +6708,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6729,7 +6741,7 @@
       <c r="I21" t="n">
         <v>4.42</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K21" t="n">
@@ -6742,13 +6754,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6775,7 +6787,7 @@
       <c r="I22" t="n">
         <v>5.705</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K22" t="n">
@@ -6788,13 +6800,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6821,7 +6833,7 @@
       <c r="I23" t="n">
         <v>5.74</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="K23" t="n">
@@ -6834,13 +6846,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6867,7 +6879,7 @@
       <c r="I24" t="n">
         <v>6.32</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K24" t="n">
@@ -6880,13 +6892,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6913,7 +6925,7 @@
       <c r="I25" t="n">
         <v>5.239999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K25" t="n">
@@ -6926,13 +6938,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6959,7 +6971,7 @@
       <c r="I26" t="n">
         <v>3.622999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K26" t="n">
@@ -6972,13 +6984,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7005,7 +7017,7 @@
       <c r="I27" t="n">
         <v>3.623</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K27" t="n">
@@ -7018,13 +7030,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7051,7 +7063,7 @@
       <c r="I28" t="n">
         <v>2.133</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="K28" t="n">
@@ -7064,13 +7076,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7097,7 +7109,7 @@
       <c r="I29" t="n">
         <v>2.213</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K29" t="n">
@@ -7110,13 +7122,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7143,7 +7155,7 @@
       <c r="I30" t="n">
         <v>2.27</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="K30" t="n">
@@ -7156,13 +7168,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7189,7 +7201,7 @@
       <c r="I31" t="n">
         <v>1.69</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K31" t="n">
@@ -7202,13 +7214,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7235,7 +7247,7 @@
       <c r="I32" t="n">
         <v>3.19</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="K32" t="n">
@@ -7248,13 +7260,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -7281,7 +7293,7 @@
       <c r="I33" t="n">
         <v>6.85</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K33" t="n">
@@ -7294,13 +7306,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7327,7 +7339,7 @@
       <c r="I34" t="n">
         <v>6.87</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="K34" t="n">
@@ -7340,13 +7352,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7373,7 +7385,7 @@
       <c r="I35" t="n">
         <v>8.209999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K35" t="n">
@@ -7386,13 +7398,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7419,7 +7431,7 @@
       <c r="I36" t="n">
         <v>8.06</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K36" t="n">
@@ -7432,13 +7444,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7465,7 +7477,7 @@
       <c r="I37" t="n">
         <v>5.32</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K37" t="n">
@@ -7478,13 +7490,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7511,7 +7523,7 @@
       <c r="I38" t="n">
         <v>5.23</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K38" t="n">
@@ -7524,13 +7536,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7557,7 +7569,7 @@
       <c r="I39" t="n">
         <v>4.62</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="K39" t="n">
@@ -7570,13 +7582,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7603,7 +7615,7 @@
       <c r="I40" t="n">
         <v>4.66</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K40" t="n">
@@ -7616,13 +7628,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7649,7 +7661,7 @@
       <c r="I41" t="n">
         <v>3.99</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="K41" t="n">
@@ -7662,13 +7674,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7695,7 +7707,7 @@
       <c r="I42" t="n">
         <v>-10.25</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K42" t="n">
@@ -7708,13 +7720,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7741,7 +7753,7 @@
       <c r="I43" t="n">
         <v>-11.9</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="K43" t="n">
@@ -7754,13 +7766,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7787,7 +7799,7 @@
       <c r="I44" t="n">
         <v>-14.92</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K44" t="n">
@@ -7800,13 +7812,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7833,7 +7845,7 @@
       <c r="I45" t="n">
         <v>-15.13</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K45" t="n">
@@ -7846,13 +7858,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7879,7 +7891,7 @@
       <c r="I46" t="n">
         <v>-1.250000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K46" t="n">
@@ -7892,13 +7904,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7925,7 +7937,7 @@
       <c r="I47" t="n">
         <v>11.74</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K47" t="n">
@@ -7938,13 +7950,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7971,7 +7983,7 @@
       <c r="I48" t="n">
         <v>14.19</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K48" t="n">
@@ -7984,13 +7996,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8017,7 +8029,7 @@
       <c r="I49" t="n">
         <v>15.24</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K49" t="n">
@@ -8030,13 +8042,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8063,7 +8075,7 @@
       <c r="I50" t="n">
         <v>17.1</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K50" t="n">
@@ -8076,13 +8088,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8109,7 +8121,7 @@
       <c r="I51" t="n">
         <v>15.05</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K51" t="n">
@@ -8122,13 +8134,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8155,7 +8167,7 @@
       <c r="I52" t="n">
         <v>23.02</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K52" t="n">
@@ -8168,13 +8180,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8201,7 +8213,7 @@
       <c r="I53" t="n">
         <v>28.12</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K53" t="n">
@@ -8214,13 +8226,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8247,7 +8259,7 @@
       <c r="I54" t="n">
         <v>32.72</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K54" t="n">
@@ -8260,13 +8272,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8293,7 +8305,7 @@
       <c r="I55" t="n">
         <v>27.09</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K55" t="n">
@@ -8306,13 +8318,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8339,7 +8351,7 @@
       <c r="I56" t="n">
         <v>26.31</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K56" t="n">
@@ -8352,13 +8364,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -8385,7 +8397,7 @@
       <c r="I57" t="n">
         <v>23.63</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K57" t="n">
@@ -8398,13 +8410,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -8431,7 +8443,7 @@
       <c r="I58" t="n">
         <v>20.12</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K58" t="n">
@@ -8444,13 +8456,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -8477,7 +8489,7 @@
       <c r="I59" t="n">
         <v>19.13</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K59" t="n">
@@ -8490,13 +8502,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -8523,7 +8535,7 @@
       <c r="I60" t="n">
         <v>12.72</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="K60" t="n">
@@ -8536,13 +8548,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -8569,7 +8581,7 @@
       <c r="I61" t="n">
         <v>10.08</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K61" t="n">
@@ -8582,13 +8594,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -8615,7 +8627,7 @@
       <c r="I62" t="n">
         <v>7.259999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K62" t="n">
@@ -8628,13 +8640,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -8661,7 +8673,7 @@
       <c r="I63" t="n">
         <v>6.889999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K63" t="n">
@@ -8674,13 +8686,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -8707,7 +8719,7 @@
       <c r="I64" t="n">
         <v>9.529999999999998</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K64" t="n">
@@ -8720,13 +8732,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -8753,7 +8765,7 @@
       <c r="I65" t="n">
         <v>13.22</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K65" t="n">
@@ -8766,13 +8778,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -8799,7 +8811,7 @@
       <c r="I66" t="n">
         <v>15.19</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K66" t="n">
@@ -8812,13 +8824,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -8845,7 +8857,7 @@
       <c r="I67" t="n">
         <v>28.96</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K67" t="n">
@@ -8882,52 +8894,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="C2" t="n">
@@ -8956,10 +8968,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C3" t="n">
@@ -8988,10 +9000,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40954</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C4" t="n">
@@ -9020,10 +9032,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="C5" t="n">
@@ -9052,10 +9064,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C6" t="n">
@@ -9084,10 +9096,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="C7" t="n">
@@ -9116,10 +9128,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C8" t="n">
@@ -9148,10 +9160,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C9" t="n">
@@ -9180,10 +9192,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C10" t="n">
@@ -9212,10 +9224,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C11" t="n">
@@ -9244,10 +9256,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C12" t="n">
@@ -9276,10 +9288,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C13" t="n">
@@ -9308,10 +9320,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C14" t="n">
@@ -9340,10 +9352,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C15" t="n">
@@ -9372,10 +9384,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C16" t="n">
@@ -9404,10 +9416,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C17" t="n">
@@ -9436,10 +9448,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="C18" t="n">
@@ -9468,10 +9480,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C19" t="n">
@@ -9500,10 +9512,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C20" t="n">
@@ -9532,10 +9544,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C21" t="n">
@@ -9564,10 +9576,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C22" t="n">
@@ -9596,10 +9608,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42670</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="C23" t="n">
@@ -9628,10 +9640,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42779</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C24" t="n">
@@ -9660,10 +9672,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42852</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="C25" t="n">
@@ -9692,10 +9704,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42943</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C26" t="n">
@@ -9724,10 +9736,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="C27" t="n">
@@ -9756,10 +9768,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43147</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C28" t="n">
@@ -9788,10 +9800,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43216</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="C29" t="n">
@@ -9820,10 +9832,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C30" t="n">
@@ -9852,10 +9864,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C31" t="n">
@@ -9884,10 +9896,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C32" t="n">
@@ -9916,10 +9928,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43588</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C33" t="n">
@@ -9948,10 +9960,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="C34" t="n">
@@ -9980,10 +9992,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C35" t="n">
@@ -10012,10 +10024,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43878</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="C36" t="n">
@@ -10044,10 +10056,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C37" t="n">
@@ -10076,10 +10088,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44042</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="C38" t="n">
@@ -10108,10 +10120,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44133</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C39" t="n">
@@ -10140,10 +10152,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C40" t="n">
@@ -10172,10 +10184,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C41" t="n">
@@ -10204,10 +10216,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C42" t="n">
@@ -10236,10 +10248,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C43" t="n">
@@ -10268,10 +10280,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44607</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C44" t="n">
@@ -10300,10 +10312,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C45" t="n">
@@ -10332,10 +10344,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C46" t="n">
@@ -10364,10 +10376,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C47" t="n">
@@ -10396,10 +10408,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C48" t="n">
@@ -10428,10 +10440,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C49" t="n">
@@ -10460,10 +10472,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C50" t="n">
@@ -10492,10 +10504,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C51" t="n">
@@ -10524,10 +10536,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45345</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C52" t="n">
@@ -10556,10 +10568,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C53" t="n">
@@ -10588,10 +10600,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C54" t="n">
@@ -10620,10 +10632,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="C55" t="n">
@@ -10652,10 +10664,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45709</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C56" t="n">
@@ -10684,10 +10696,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C57" t="n">
@@ -10716,10 +10728,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C58" t="n">
@@ -10748,10 +10760,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C59" t="n">
@@ -10780,10 +10792,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C60" t="n">
@@ -10812,10 +10824,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C61" t="n">
@@ -10844,10 +10856,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46233</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C62" t="n">
@@ -10894,12 +10906,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MPC.xlsx
+++ b/salidas/empresas/MPC.xlsx
@@ -498,7 +498,7 @@
         <v>40724</v>
       </c>
       <c r="B2" t="n">
-        <v>13.5028829574585</v>
+        <v>13.50288200378418</v>
       </c>
       <c r="C2" t="n">
         <v>20.70000076293945</v>
@@ -536,7 +536,7 @@
         <v>40786</v>
       </c>
       <c r="B4" t="n">
-        <v>12.15232849121094</v>
+        <v>12.15232467651367</v>
       </c>
       <c r="C4" t="n">
         <v>18.53000068664551</v>
@@ -586,7 +586,7 @@
         <v>40847</v>
       </c>
       <c r="B6" t="n">
-        <v>11.77195644378662</v>
+        <v>11.77195835113525</v>
       </c>
       <c r="C6" t="n">
         <v>17.95000076293945</v>
@@ -611,7 +611,7 @@
         <v>40877</v>
       </c>
       <c r="B7" t="n">
-        <v>11.02185916900635</v>
+        <v>11.0218563079834</v>
       </c>
       <c r="C7" t="n">
         <v>16.69499969482422</v>
@@ -636,7 +636,7 @@
         <v>40908</v>
       </c>
       <c r="B8" t="n">
-        <v>10.988844871521</v>
+        <v>10.98884773254395</v>
       </c>
       <c r="C8" t="n">
         <v>16.64500045776367</v>
@@ -661,7 +661,7 @@
         <v>40939</v>
       </c>
       <c r="B9" t="n">
-        <v>12.61621189117432</v>
+        <v>12.6162166595459</v>
       </c>
       <c r="C9" t="n">
         <v>19.11000061035156</v>
@@ -686,7 +686,7 @@
         <v>40968</v>
       </c>
       <c r="B10" t="n">
-        <v>13.79474353790283</v>
+        <v>13.79473781585693</v>
       </c>
       <c r="C10" t="n">
         <v>20.77499961853027</v>
@@ -715,7 +715,7 @@
         <v>40999</v>
       </c>
       <c r="B11" t="n">
-        <v>14.39566993713379</v>
+        <v>14.39566898345947</v>
       </c>
       <c r="C11" t="n">
         <v>21.68000030517578</v>
@@ -744,7 +744,7 @@
         <v>41029</v>
       </c>
       <c r="B12" t="n">
-        <v>13.81466674804688</v>
+        <v>13.81465721130371</v>
       </c>
       <c r="C12" t="n">
         <v>20.80500030517578</v>
@@ -773,7 +773,7 @@
         <v>41060</v>
       </c>
       <c r="B13" t="n">
-        <v>12.05636501312256</v>
+        <v>12.05636215209961</v>
       </c>
       <c r="C13" t="n">
         <v>18.03499984741211</v>
@@ -802,7 +802,7 @@
         <v>41090</v>
       </c>
       <c r="B14" t="n">
-        <v>15.01447010040283</v>
+        <v>15.01447296142578</v>
       </c>
       <c r="C14" t="n">
         <v>22.45999908447266</v>
@@ -831,7 +831,7 @@
         <v>41121</v>
       </c>
       <c r="B15" t="n">
-        <v>15.80998134613037</v>
+        <v>15.80998229980469</v>
       </c>
       <c r="C15" t="n">
         <v>23.64999961853027</v>
@@ -860,7 +860,7 @@
         <v>41152</v>
       </c>
       <c r="B16" t="n">
-        <v>17.4204158782959</v>
+        <v>17.4204216003418</v>
       </c>
       <c r="C16" t="n">
         <v>25.875</v>
@@ -889,7 +889,7 @@
         <v>41182</v>
       </c>
       <c r="B17" t="n">
-        <v>18.37643623352051</v>
+        <v>18.37644004821777</v>
       </c>
       <c r="C17" t="n">
         <v>27.29500007629395</v>
@@ -918,7 +918,7 @@
         <v>41213</v>
       </c>
       <c r="B18" t="n">
-        <v>18.49088668823242</v>
+        <v>18.49089050292969</v>
       </c>
       <c r="C18" t="n">
         <v>27.46500015258789</v>
@@ -947,7 +947,7 @@
         <v>41243</v>
       </c>
       <c r="B19" t="n">
-        <v>20.17266464233398</v>
+        <v>20.17267036437988</v>
       </c>
       <c r="C19" t="n">
         <v>29.77000045776367</v>
@@ -976,7 +976,7 @@
         <v>41274</v>
       </c>
       <c r="B20" t="n">
-        <v>21.34494781494141</v>
+        <v>21.34494972229004</v>
       </c>
       <c r="C20" t="n">
         <v>31.5</v>
@@ -1005,7 +1005,7 @@
         <v>41305</v>
       </c>
       <c r="B21" t="n">
-        <v>25.14299201965332</v>
+        <v>25.14298820495605</v>
       </c>
       <c r="C21" t="n">
         <v>37.10499954223633</v>
@@ -1034,7 +1034,7 @@
         <v>41333</v>
       </c>
       <c r="B22" t="n">
-        <v>28.19913291931152</v>
+        <v>28.19914627075195</v>
       </c>
       <c r="C22" t="n">
         <v>41.43999862670898</v>
@@ -1063,7 +1063,7 @@
         <v>41364</v>
       </c>
       <c r="B23" t="n">
-        <v>30.48557472229004</v>
+        <v>30.48555946350098</v>
       </c>
       <c r="C23" t="n">
         <v>44.79999923706055</v>
@@ -1092,7 +1092,7 @@
         <v>41394</v>
       </c>
       <c r="B24" t="n">
-        <v>26.66125869750977</v>
+        <v>26.66126441955566</v>
       </c>
       <c r="C24" t="n">
         <v>39.18000030517578</v>
@@ -1121,7 +1121,7 @@
         <v>41425</v>
       </c>
       <c r="B25" t="n">
-        <v>28.19895172119141</v>
+        <v>28.19894790649414</v>
       </c>
       <c r="C25" t="n">
         <v>41.25</v>
@@ -1150,7 +1150,7 @@
         <v>41455</v>
       </c>
       <c r="B26" t="n">
-        <v>24.2887077331543</v>
+        <v>24.2886962890625</v>
       </c>
       <c r="C26" t="n">
         <v>35.52999877929688</v>
@@ -1179,7 +1179,7 @@
         <v>41486</v>
       </c>
       <c r="B27" t="n">
-        <v>25.0645923614502</v>
+        <v>25.06460762023926</v>
       </c>
       <c r="C27" t="n">
         <v>36.66500091552734</v>
@@ -1208,7 +1208,7 @@
         <v>41517</v>
       </c>
       <c r="B28" t="n">
-        <v>24.93392181396484</v>
+        <v>24.93392562866211</v>
       </c>
       <c r="C28" t="n">
         <v>36.25500106811523</v>
@@ -1237,7 +1237,7 @@
         <v>41547</v>
       </c>
       <c r="B29" t="n">
-        <v>22.11763572692871</v>
+        <v>22.11763763427734</v>
       </c>
       <c r="C29" t="n">
         <v>32.15999984741211</v>
@@ -1266,7 +1266,7 @@
         <v>41578</v>
       </c>
       <c r="B30" t="n">
-        <v>24.64162635803223</v>
+        <v>24.64163970947266</v>
       </c>
       <c r="C30" t="n">
         <v>35.83000183105469</v>
@@ -1295,7 +1295,7 @@
         <v>41608</v>
       </c>
       <c r="B31" t="n">
-        <v>28.60407638549805</v>
+        <v>28.60408210754395</v>
       </c>
       <c r="C31" t="n">
         <v>41.36999893188477</v>
@@ -1324,7 +1324,7 @@
         <v>41639</v>
       </c>
       <c r="B32" t="n">
-        <v>31.71200942993164</v>
+        <v>31.71201515197754</v>
       </c>
       <c r="C32" t="n">
         <v>45.8650016784668</v>
@@ -1353,7 +1353,7 @@
         <v>41670</v>
       </c>
       <c r="B33" t="n">
-        <v>30.09408950805664</v>
+        <v>30.09410858154297</v>
       </c>
       <c r="C33" t="n">
         <v>43.52500152587891</v>
@@ -1382,7 +1382,7 @@
         <v>41698</v>
       </c>
       <c r="B34" t="n">
-        <v>29.18289184570312</v>
+        <v>29.18289566040039</v>
       </c>
       <c r="C34" t="n">
         <v>42</v>
@@ -1411,7 +1411,7 @@
         <v>41729</v>
       </c>
       <c r="B35" t="n">
-        <v>30.23903656005859</v>
+        <v>30.23903846740723</v>
       </c>
       <c r="C35" t="n">
         <v>43.52000045776367</v>
@@ -1440,7 +1440,7 @@
         <v>41759</v>
       </c>
       <c r="B36" t="n">
-        <v>32.29226684570312</v>
+        <v>32.29227066040039</v>
       </c>
       <c r="C36" t="n">
         <v>46.47499847412109</v>
@@ -1469,7 +1469,7 @@
         <v>41790</v>
       </c>
       <c r="B37" t="n">
-        <v>31.20262336730957</v>
+        <v>31.20262718200684</v>
       </c>
       <c r="C37" t="n">
         <v>44.69499969482422</v>
@@ -1498,7 +1498,7 @@
         <v>41820</v>
       </c>
       <c r="B38" t="n">
-        <v>27.25124549865723</v>
+        <v>27.25125503540039</v>
       </c>
       <c r="C38" t="n">
         <v>39.03499984741211</v>
@@ -1527,7 +1527,7 @@
         <v>41851</v>
       </c>
       <c r="B39" t="n">
-        <v>29.13966178894043</v>
+        <v>29.13967323303223</v>
       </c>
       <c r="C39" t="n">
         <v>41.7400016784668</v>
@@ -1556,7 +1556,7 @@
         <v>41882</v>
       </c>
       <c r="B40" t="n">
-        <v>31.94743156433105</v>
+        <v>31.94742393493652</v>
       </c>
       <c r="C40" t="n">
         <v>45.50500106811523</v>
@@ -1585,7 +1585,7 @@
         <v>41912</v>
       </c>
       <c r="B41" t="n">
-        <v>29.72188377380371</v>
+        <v>29.72188568115234</v>
       </c>
       <c r="C41" t="n">
         <v>42.33499908447266</v>
@@ -1614,7 +1614,7 @@
         <v>41943</v>
       </c>
       <c r="B42" t="n">
-        <v>31.90882873535156</v>
+        <v>31.90881538391113</v>
       </c>
       <c r="C42" t="n">
         <v>45.45000076293945</v>
@@ -1643,7 +1643,7 @@
         <v>41973</v>
       </c>
       <c r="B43" t="n">
-        <v>31.79657554626465</v>
+        <v>31.79656028747559</v>
       </c>
       <c r="C43" t="n">
         <v>45.04499816894531</v>
@@ -1672,7 +1672,7 @@
         <v>42004</v>
       </c>
       <c r="B44" t="n">
-        <v>31.8565731048584</v>
+        <v>31.85657501220703</v>
       </c>
       <c r="C44" t="n">
         <v>45.13000106811523</v>
@@ -1701,7 +1701,7 @@
         <v>42035</v>
       </c>
       <c r="B45" t="n">
-        <v>32.67891311645508</v>
+        <v>32.67893600463867</v>
       </c>
       <c r="C45" t="n">
         <v>46.29499816894531</v>
@@ -1730,7 +1730,7 @@
         <v>42063</v>
       </c>
       <c r="B46" t="n">
-        <v>37.24258804321289</v>
+        <v>37.24258422851562</v>
       </c>
       <c r="C46" t="n">
         <v>52.5</v>
@@ -1759,7 +1759,7 @@
         <v>42094</v>
       </c>
       <c r="B47" t="n">
-        <v>36.31682586669922</v>
+        <v>36.31683349609375</v>
       </c>
       <c r="C47" t="n">
         <v>51.19499969482422</v>
@@ -1788,7 +1788,7 @@
         <v>42124</v>
       </c>
       <c r="B48" t="n">
-        <v>34.96192169189453</v>
+        <v>34.96191024780273</v>
       </c>
       <c r="C48" t="n">
         <v>49.28499984741211</v>
@@ -1817,7 +1817,7 @@
         <v>42155</v>
       </c>
       <c r="B49" t="n">
-        <v>36.87457656860352</v>
+        <v>36.87458038330078</v>
       </c>
       <c r="C49" t="n">
         <v>51.72999954223633</v>
@@ -1875,7 +1875,7 @@
         <v>42216</v>
       </c>
       <c r="B51" t="n">
-        <v>38.97029113769531</v>
+        <v>38.97030258178711</v>
       </c>
       <c r="C51" t="n">
         <v>54.66999816894531</v>
@@ -1904,7 +1904,7 @@
         <v>42247</v>
       </c>
       <c r="B52" t="n">
-        <v>33.91889572143555</v>
+        <v>33.91888427734375</v>
       </c>
       <c r="C52" t="n">
         <v>47.31000137329102</v>
@@ -1962,7 +1962,7 @@
         <v>42308</v>
       </c>
       <c r="B54" t="n">
-        <v>37.13798522949219</v>
+        <v>37.13799285888672</v>
       </c>
       <c r="C54" t="n">
         <v>51.79999923706055</v>
@@ -1991,7 +1991,7 @@
         <v>42338</v>
       </c>
       <c r="B55" t="n">
-        <v>42.12818145751953</v>
+        <v>42.12816619873047</v>
       </c>
       <c r="C55" t="n">
         <v>58.40999984741211</v>
@@ -2020,7 +2020,7 @@
         <v>42369</v>
       </c>
       <c r="B56" t="n">
-        <v>37.38956832885742</v>
+        <v>37.38956069946289</v>
       </c>
       <c r="C56" t="n">
         <v>51.84000015258789</v>
@@ -2049,7 +2049,7 @@
         <v>42400</v>
       </c>
       <c r="B57" t="n">
-        <v>30.1410083770752</v>
+        <v>30.1409912109375</v>
       </c>
       <c r="C57" t="n">
         <v>41.79000091552734</v>
@@ -2107,7 +2107,7 @@
         <v>42460</v>
       </c>
       <c r="B59" t="n">
-        <v>27.0973014831543</v>
+        <v>27.09730529785156</v>
       </c>
       <c r="C59" t="n">
         <v>37.18000030517578</v>
@@ -2136,7 +2136,7 @@
         <v>42490</v>
       </c>
       <c r="B60" t="n">
-        <v>28.4820499420166</v>
+        <v>28.48205184936523</v>
       </c>
       <c r="C60" t="n">
         <v>39.08000183105469</v>
@@ -2165,7 +2165,7 @@
         <v>42521</v>
       </c>
       <c r="B61" t="n">
-        <v>25.61555290222168</v>
+        <v>25.61555862426758</v>
       </c>
       <c r="C61" t="n">
         <v>34.83000183105469</v>
@@ -2194,7 +2194,7 @@
         <v>42551</v>
       </c>
       <c r="B62" t="n">
-        <v>27.91750717163086</v>
+        <v>27.91750144958496</v>
       </c>
       <c r="C62" t="n">
         <v>37.95999908447266</v>
@@ -2223,7 +2223,7 @@
         <v>42582</v>
       </c>
       <c r="B63" t="n">
-        <v>28.96918296813965</v>
+        <v>28.96919059753418</v>
       </c>
       <c r="C63" t="n">
         <v>39.38999938964844</v>
@@ -2252,7 +2252,7 @@
         <v>42613</v>
       </c>
       <c r="B64" t="n">
-        <v>31.53597068786621</v>
+        <v>31.53596115112305</v>
       </c>
       <c r="C64" t="n">
         <v>42.5099983215332</v>
@@ -2281,7 +2281,7 @@
         <v>42643</v>
       </c>
       <c r="B65" t="n">
-        <v>30.11161804199219</v>
+        <v>30.11161994934082</v>
       </c>
       <c r="C65" t="n">
         <v>40.59000015258789</v>
@@ -2310,7 +2310,7 @@
         <v>42674</v>
       </c>
       <c r="B66" t="n">
-        <v>32.33716583251953</v>
+        <v>32.3371696472168</v>
       </c>
       <c r="C66" t="n">
         <v>43.59000015258789</v>
@@ -2339,7 +2339,7 @@
         <v>42704</v>
       </c>
       <c r="B67" t="n">
-        <v>35.16971588134766</v>
+        <v>35.16971969604492</v>
       </c>
       <c r="C67" t="n">
         <v>47.02000045776367</v>
@@ -2397,7 +2397,7 @@
         <v>42766</v>
       </c>
       <c r="B69" t="n">
-        <v>35.94012451171875</v>
+        <v>35.94013595581055</v>
       </c>
       <c r="C69" t="n">
         <v>48.04999923706055</v>
@@ -2484,7 +2484,7 @@
         <v>42855</v>
       </c>
       <c r="B72" t="n">
-        <v>38.37654113769531</v>
+        <v>38.37653350830078</v>
       </c>
       <c r="C72" t="n">
         <v>50.93999862670898</v>
@@ -2513,7 +2513,7 @@
         <v>42886</v>
       </c>
       <c r="B73" t="n">
-        <v>39.47505569458008</v>
+        <v>39.47505950927734</v>
       </c>
       <c r="C73" t="n">
         <v>52.04000091552734</v>
@@ -2542,7 +2542,7 @@
         <v>42916</v>
       </c>
       <c r="B74" t="n">
-        <v>39.69503021240234</v>
+        <v>39.69504547119141</v>
       </c>
       <c r="C74" t="n">
         <v>52.33000183105469</v>
@@ -2571,7 +2571,7 @@
         <v>42947</v>
       </c>
       <c r="B75" t="n">
-        <v>42.47133255004883</v>
+        <v>42.47134399414062</v>
       </c>
       <c r="C75" t="n">
         <v>55.9900016784668</v>
@@ -2600,7 +2600,7 @@
         <v>42978</v>
       </c>
       <c r="B76" t="n">
-        <v>40.0935173034668</v>
+        <v>40.09353256225586</v>
       </c>
       <c r="C76" t="n">
         <v>52.45000076293945</v>
@@ -2629,7 +2629,7 @@
         <v>43008</v>
       </c>
       <c r="B77" t="n">
-        <v>42.86834716796875</v>
+        <v>42.86835479736328</v>
       </c>
       <c r="C77" t="n">
         <v>56.08000183105469</v>
@@ -2687,7 +2687,7 @@
         <v>43069</v>
       </c>
       <c r="B79" t="n">
-        <v>48.18181610107422</v>
+        <v>48.18181228637695</v>
       </c>
       <c r="C79" t="n">
         <v>62.63000106811523</v>
@@ -2716,7 +2716,7 @@
         <v>43100</v>
       </c>
       <c r="B80" t="n">
-        <v>50.75900650024414</v>
+        <v>50.75900268554688</v>
       </c>
       <c r="C80" t="n">
         <v>65.98000335693359</v>
@@ -2745,7 +2745,7 @@
         <v>43131</v>
       </c>
       <c r="B81" t="n">
-        <v>53.2900276184082</v>
+        <v>53.29002380371094</v>
       </c>
       <c r="C81" t="n">
         <v>69.26999664306641</v>
@@ -2774,7 +2774,7 @@
         <v>43159</v>
       </c>
       <c r="B82" t="n">
-        <v>49.61791610717773</v>
+        <v>49.617919921875</v>
       </c>
       <c r="C82" t="n">
         <v>64.05999755859375</v>
@@ -2803,7 +2803,7 @@
         <v>43190</v>
       </c>
       <c r="B83" t="n">
-        <v>56.62765884399414</v>
+        <v>56.62763595581055</v>
       </c>
       <c r="C83" t="n">
         <v>73.11000061035156</v>
@@ -2861,7 +2861,7 @@
         <v>43251</v>
       </c>
       <c r="B85" t="n">
-        <v>61.57456970214844</v>
+        <v>61.57454681396484</v>
       </c>
       <c r="C85" t="n">
         <v>79.02999877929688</v>
@@ -2890,7 +2890,7 @@
         <v>43281</v>
       </c>
       <c r="B86" t="n">
-        <v>54.66369247436523</v>
+        <v>54.66367721557617</v>
       </c>
       <c r="C86" t="n">
         <v>70.16000366210938</v>
@@ -2919,7 +2919,7 @@
         <v>43312</v>
       </c>
       <c r="B87" t="n">
-        <v>62.97698974609375</v>
+        <v>62.97698593139648</v>
       </c>
       <c r="C87" t="n">
         <v>80.83000183105469</v>
@@ -2948,7 +2948,7 @@
         <v>43343</v>
       </c>
       <c r="B88" t="n">
-        <v>64.48479461669922</v>
+        <v>64.48480224609375</v>
       </c>
       <c r="C88" t="n">
         <v>82.29000091552734</v>
@@ -2977,7 +2977,7 @@
         <v>43373</v>
       </c>
       <c r="B89" t="n">
-        <v>62.66677856445312</v>
+        <v>62.66678237915039</v>
       </c>
       <c r="C89" t="n">
         <v>79.97000122070312</v>
@@ -3006,7 +3006,7 @@
         <v>43404</v>
       </c>
       <c r="B90" t="n">
-        <v>55.20662307739258</v>
+        <v>55.20662689208984</v>
       </c>
       <c r="C90" t="n">
         <v>70.44999694824219</v>
@@ -3035,7 +3035,7 @@
         <v>43434</v>
       </c>
       <c r="B91" t="n">
-        <v>51.43436813354492</v>
+        <v>51.43436431884766</v>
       </c>
       <c r="C91" t="n">
         <v>65.16000366210938</v>
@@ -3064,7 +3064,7 @@
         <v>43465</v>
       </c>
       <c r="B92" t="n">
-        <v>46.57983779907227</v>
+        <v>46.57983016967773</v>
       </c>
       <c r="C92" t="n">
         <v>59.0099983215332</v>
@@ -3122,7 +3122,7 @@
         <v>43524</v>
       </c>
       <c r="B94" t="n">
-        <v>49.3493537902832</v>
+        <v>49.34934616088867</v>
       </c>
       <c r="C94" t="n">
         <v>62.0099983215332</v>
@@ -3151,7 +3151,7 @@
         <v>43555</v>
       </c>
       <c r="B95" t="n">
-        <v>47.63036727905273</v>
+        <v>47.63036346435547</v>
       </c>
       <c r="C95" t="n">
         <v>59.84999847412109</v>
@@ -3209,7 +3209,7 @@
         <v>43616</v>
       </c>
       <c r="B97" t="n">
-        <v>36.98217010498047</v>
+        <v>36.98218536376953</v>
       </c>
       <c r="C97" t="n">
         <v>45.9900016784668</v>
@@ -3238,7 +3238,7 @@
         <v>43646</v>
       </c>
       <c r="B98" t="n">
-        <v>44.93508529663086</v>
+        <v>44.93507766723633</v>
       </c>
       <c r="C98" t="n">
         <v>55.88000106811523</v>
@@ -3267,7 +3267,7 @@
         <v>43677</v>
       </c>
       <c r="B99" t="n">
-        <v>45.34516906738281</v>
+        <v>45.34518432617188</v>
       </c>
       <c r="C99" t="n">
         <v>56.38999938964844</v>
@@ -3296,7 +3296,7 @@
         <v>43708</v>
       </c>
       <c r="B100" t="n">
-        <v>40.01508712768555</v>
+        <v>40.01507568359375</v>
       </c>
       <c r="C100" t="n">
         <v>49.20999908447266</v>
@@ -3325,7 +3325,7 @@
         <v>43738</v>
       </c>
       <c r="B101" t="n">
-        <v>49.39882659912109</v>
+        <v>49.39883041381836</v>
       </c>
       <c r="C101" t="n">
         <v>60.75</v>
@@ -3354,7 +3354,7 @@
         <v>43769</v>
       </c>
       <c r="B102" t="n">
-        <v>52.00090789794922</v>
+        <v>52.00090408325195</v>
       </c>
       <c r="C102" t="n">
         <v>63.95000076293945</v>
@@ -3441,7 +3441,7 @@
         <v>43861</v>
       </c>
       <c r="B105" t="n">
-        <v>44.68357086181641</v>
+        <v>44.6835823059082</v>
       </c>
       <c r="C105" t="n">
         <v>54.5</v>
@@ -3528,7 +3528,7 @@
         <v>43951</v>
       </c>
       <c r="B108" t="n">
-        <v>26.56598281860352</v>
+        <v>26.56598472595215</v>
       </c>
       <c r="C108" t="n">
         <v>32.08000183105469</v>
@@ -3557,7 +3557,7 @@
         <v>43982</v>
       </c>
       <c r="B109" t="n">
-        <v>29.59108352661133</v>
+        <v>29.59108543395996</v>
       </c>
       <c r="C109" t="n">
         <v>35.13999938964844</v>
@@ -3584,7 +3584,7 @@
         <v>44012</v>
       </c>
       <c r="B110" t="n">
-        <v>31.47736930847168</v>
+        <v>31.47736549377441</v>
       </c>
       <c r="C110" t="n">
         <v>37.38000106811523</v>
@@ -3638,7 +3638,7 @@
         <v>44074</v>
       </c>
       <c r="B112" t="n">
-        <v>30.31547927856445</v>
+        <v>30.31548118591309</v>
       </c>
       <c r="C112" t="n">
         <v>35.45999908447266</v>
@@ -3665,7 +3665,7 @@
         <v>44104</v>
       </c>
       <c r="B113" t="n">
-        <v>25.08336639404297</v>
+        <v>25.08337020874023</v>
       </c>
       <c r="C113" t="n">
         <v>29.34000015258789</v>
@@ -3692,7 +3692,7 @@
         <v>44135</v>
       </c>
       <c r="B114" t="n">
-        <v>25.22015380859375</v>
+        <v>25.22015953063965</v>
       </c>
       <c r="C114" t="n">
         <v>29.5</v>
@@ -3719,7 +3719,7 @@
         <v>44165</v>
       </c>
       <c r="B115" t="n">
-        <v>33.719482421875</v>
+        <v>33.71947860717773</v>
       </c>
       <c r="C115" t="n">
         <v>38.88000106811523</v>
@@ -3773,7 +3773,7 @@
         <v>44227</v>
       </c>
       <c r="B117" t="n">
-        <v>37.43140411376953</v>
+        <v>37.43139266967773</v>
       </c>
       <c r="C117" t="n">
         <v>43.15999984741211</v>
@@ -3800,7 +3800,7 @@
         <v>44255</v>
       </c>
       <c r="B118" t="n">
-        <v>47.92113494873047</v>
+        <v>47.9211311340332</v>
       </c>
       <c r="C118" t="n">
         <v>54.61999893188477</v>
@@ -3827,7 +3827,7 @@
         <v>44286</v>
       </c>
       <c r="B119" t="n">
-        <v>46.92972183227539</v>
+        <v>46.92973327636719</v>
       </c>
       <c r="C119" t="n">
         <v>53.4900016784668</v>
@@ -3854,7 +3854,7 @@
         <v>44316</v>
       </c>
       <c r="B120" t="n">
-        <v>48.82480621337891</v>
+        <v>48.82482147216797</v>
       </c>
       <c r="C120" t="n">
         <v>55.65000152587891</v>
@@ -3908,7 +3908,7 @@
         <v>44377</v>
       </c>
       <c r="B122" t="n">
-        <v>53.51432800292969</v>
+        <v>53.51432037353516</v>
       </c>
       <c r="C122" t="n">
         <v>60.41999816894531</v>
@@ -3935,7 +3935,7 @@
         <v>44408</v>
       </c>
       <c r="B123" t="n">
-        <v>48.90865707397461</v>
+        <v>48.90865325927734</v>
       </c>
       <c r="C123" t="n">
         <v>55.22000122070312</v>
@@ -3962,7 +3962,7 @@
         <v>44439</v>
       </c>
       <c r="B124" t="n">
-        <v>53.02254104614258</v>
+        <v>53.02252578735352</v>
       </c>
       <c r="C124" t="n">
         <v>59.27000045776367</v>
@@ -3991,7 +3991,7 @@
         <v>44469</v>
       </c>
       <c r="B125" t="n">
-        <v>55.29480361938477</v>
+        <v>55.29480743408203</v>
       </c>
       <c r="C125" t="n">
         <v>61.81000137329102</v>
@@ -4020,7 +4020,7 @@
         <v>44500</v>
       </c>
       <c r="B126" t="n">
-        <v>58.98053359985352</v>
+        <v>58.98052597045898</v>
       </c>
       <c r="C126" t="n">
         <v>65.93000030517578</v>
@@ -4049,7 +4049,7 @@
         <v>44530</v>
       </c>
       <c r="B127" t="n">
-        <v>54.91772079467773</v>
+        <v>54.91772842407227</v>
       </c>
       <c r="C127" t="n">
         <v>60.84999847412109</v>
@@ -4107,7 +4107,7 @@
         <v>44592</v>
       </c>
       <c r="B129" t="n">
-        <v>64.75506591796875</v>
+        <v>64.75508117675781</v>
       </c>
       <c r="C129" t="n">
         <v>71.75</v>
@@ -4165,7 +4165,7 @@
         <v>44651</v>
       </c>
       <c r="B131" t="n">
-        <v>77.73416137695312</v>
+        <v>77.73415374755859</v>
       </c>
       <c r="C131" t="n">
         <v>85.5</v>
@@ -4194,7 +4194,7 @@
         <v>44681</v>
       </c>
       <c r="B132" t="n">
-        <v>79.33430480957031</v>
+        <v>79.33428955078125</v>
       </c>
       <c r="C132" t="n">
         <v>87.26000213623047</v>
@@ -4223,7 +4223,7 @@
         <v>44712</v>
       </c>
       <c r="B133" t="n">
-        <v>93.10432434082031</v>
+        <v>93.10431671142578</v>
       </c>
       <c r="C133" t="n">
         <v>101.7900009155273</v>
@@ -4310,7 +4310,7 @@
         <v>44804</v>
       </c>
       <c r="B136" t="n">
-        <v>92.71445465087891</v>
+        <v>92.71443176269531</v>
       </c>
       <c r="C136" t="n">
         <v>100.75</v>
@@ -4397,7 +4397,7 @@
         <v>44895</v>
       </c>
       <c r="B139" t="n">
-        <v>112.7966384887695</v>
+        <v>112.796630859375</v>
       </c>
       <c r="C139" t="n">
         <v>121.8099975585938</v>
@@ -4455,7 +4455,7 @@
         <v>44957</v>
       </c>
       <c r="B141" t="n">
-        <v>119.010139465332</v>
+        <v>119.0101318359375</v>
       </c>
       <c r="C141" t="n">
         <v>128.5200042724609</v>
@@ -4484,7 +4484,7 @@
         <v>44985</v>
       </c>
       <c r="B142" t="n">
-        <v>115.1253814697266</v>
+        <v>115.1254043579102</v>
       </c>
       <c r="C142" t="n">
         <v>123.5999984741211</v>
@@ -4513,7 +4513,7 @@
         <v>45016</v>
       </c>
       <c r="B143" t="n">
-        <v>125.5853805541992</v>
+        <v>125.5853958129883</v>
       </c>
       <c r="C143" t="n">
         <v>134.8300018310547</v>
@@ -4542,7 +4542,7 @@
         <v>45046</v>
       </c>
       <c r="B144" t="n">
-        <v>113.6350860595703</v>
+        <v>113.6350936889648</v>
       </c>
       <c r="C144" t="n">
         <v>122</v>
@@ -4571,7 +4571,7 @@
         <v>45077</v>
       </c>
       <c r="B145" t="n">
-        <v>98.38385772705078</v>
+        <v>98.38385009765625</v>
       </c>
       <c r="C145" t="n">
         <v>104.9100036621094</v>
@@ -4629,7 +4629,7 @@
         <v>45138</v>
       </c>
       <c r="B147" t="n">
-        <v>124.7452163696289</v>
+        <v>124.7452011108398</v>
       </c>
       <c r="C147" t="n">
         <v>133.0200042724609</v>
@@ -4658,7 +4658,7 @@
         <v>45169</v>
       </c>
       <c r="B148" t="n">
-        <v>134.5681304931641</v>
+        <v>134.5681610107422</v>
       </c>
       <c r="C148" t="n">
         <v>142.7700042724609</v>
@@ -4687,7 +4687,7 @@
         <v>45199</v>
       </c>
       <c r="B149" t="n">
-        <v>142.6457977294922</v>
+        <v>142.6457824707031</v>
       </c>
       <c r="C149" t="n">
         <v>151.3399963378906</v>
@@ -4745,7 +4745,7 @@
         <v>45260</v>
       </c>
       <c r="B151" t="n">
-        <v>141.3935546875</v>
+        <v>141.3935241699219</v>
       </c>
       <c r="C151" t="n">
         <v>149.1900024414062</v>
@@ -4832,7 +4832,7 @@
         <v>45351</v>
       </c>
       <c r="B154" t="n">
-        <v>161.1683502197266</v>
+        <v>161.1683807373047</v>
       </c>
       <c r="C154" t="n">
         <v>169.2299957275391</v>
@@ -4861,7 +4861,7 @@
         <v>45382</v>
       </c>
       <c r="B155" t="n">
-        <v>191.9011077880859</v>
+        <v>191.901123046875</v>
       </c>
       <c r="C155" t="n">
         <v>201.5</v>
@@ -4890,7 +4890,7 @@
         <v>45412</v>
       </c>
       <c r="B156" t="n">
-        <v>173.0633697509766</v>
+        <v>173.0634002685547</v>
       </c>
       <c r="C156" t="n">
         <v>181.7200012207031</v>
@@ -4977,7 +4977,7 @@
         <v>45504</v>
       </c>
       <c r="B159" t="n">
-        <v>169.3880310058594</v>
+        <v>169.3880462646484</v>
       </c>
       <c r="C159" t="n">
         <v>177.0200042724609</v>
@@ -5006,7 +5006,7 @@
         <v>45535</v>
       </c>
       <c r="B160" t="n">
-        <v>170.3024597167969</v>
+        <v>170.3024749755859</v>
       </c>
       <c r="C160" t="n">
         <v>177.1199951171875</v>
@@ -5122,7 +5122,7 @@
         <v>45657</v>
       </c>
       <c r="B164" t="n">
-        <v>134.9035339355469</v>
+        <v>134.9035491943359</v>
       </c>
       <c r="C164" t="n">
         <v>139.5</v>
@@ -5180,7 +5180,7 @@
         <v>45716</v>
       </c>
       <c r="B166" t="n">
-        <v>146.0674743652344</v>
+        <v>146.0674591064453</v>
       </c>
       <c r="C166" t="n">
         <v>150.1799926757812</v>
@@ -5238,7 +5238,7 @@
         <v>45777</v>
       </c>
       <c r="B168" t="n">
-        <v>133.6471557617188</v>
+        <v>133.6471710205078</v>
       </c>
       <c r="C168" t="n">
         <v>137.4100036621094</v>
@@ -5267,7 +5267,7 @@
         <v>45808</v>
       </c>
       <c r="B169" t="n">
-        <v>157.2240295410156</v>
+        <v>157.2240447998047</v>
       </c>
       <c r="C169" t="n">
         <v>160.7400054931641</v>
@@ -5296,7 +5296,7 @@
         <v>45838</v>
       </c>
       <c r="B170" t="n">
-        <v>162.4765777587891</v>
+        <v>162.4765930175781</v>
       </c>
       <c r="C170" t="n">
         <v>166.1100006103516</v>
@@ -5354,7 +5354,7 @@
         <v>45900</v>
       </c>
       <c r="B172" t="n">
-        <v>176.7576446533203</v>
+        <v>176.7576293945312</v>
       </c>
       <c r="C172" t="n">
         <v>179.7100067138672</v>
